--- a/04_DESIGN_TABLES/DesignTable_6803_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6803_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ6"/>
+  <dimension ref="A1:BZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,32 +1064,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-04-04-04-NWO-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.45</v>
+        <v>0.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4375</v>
+        <v>0.21875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.107</v>
+        <v>0.075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3553</v>
+        <v>0.2608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.386</v>
+        <v>0.182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1114</v>
+        <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1098,28 +1098,28 @@
         <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4375</v>
+        <v>0.21875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.107</v>
+        <v>0.075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3553</v>
+        <v>0.2608</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.386</v>
+        <v>0.182</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1114</v>
+        <v>0.0795</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
@@ -1128,154 +1128,154 @@
         <v>37</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4</v>
+        <v>0.2252</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.505</v>
+        <v>0.285</v>
       </c>
       <c r="AB3" t="n">
         <v>75</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.58735</v>
+        <v>0.33332</v>
       </c>
       <c r="AD3" t="n">
         <v>75</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.505</v>
+        <v>0.285</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5775</v>
+        <v>0.325</v>
       </c>
       <c r="AH3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AU3" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI3" t="n">
-        <v>0.3865</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AV3" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.875</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.3553</v>
+        <v>0.2608</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.03866</v>
+        <v>0.02706</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01786</v>
+        <v>0.0125</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.875</v>
+        <v>0.4375</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.391</v>
+        <v>0.265</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.03866</v>
+        <v>0.02706</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01786</v>
+        <v>0.0125</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-04-04-04-NWO-FG</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/8-14 JIC x 7/8-14 JIC x 7/8-14 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/16-20 JIC x 7/16-20 JIC x 7/16-20 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7/8-14 (adjustable male ORB)</t>
+          <t>7/16-20 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1310,44 +1310,44 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1 = Air-Way 6801 ORB_I3 for -10 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p059-t02: agrees on LEG1@DRIVE, LEG2@DRIVE, LEG3@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE, D3@BORE | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 0.73 = Air-Way 6801 ORB_I3 for -04 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-04-04-04-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-04-04-06-NWO-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.53125</v>
+        <v>0.281</v>
       </c>
       <c r="D4" t="n">
-        <v>0.53125</v>
+        <v>0.21875</v>
       </c>
       <c r="E4" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3895</v>
+        <v>0.2608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4715</v>
+        <v>0.182</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1299</v>
+        <v>0.0795</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1851</v>
+        <v>0.1135</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1356,28 +1356,28 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.53125</v>
+        <v>0.281</v>
       </c>
       <c r="N4" t="n">
-        <v>0.53125</v>
+        <v>0.21875</v>
       </c>
       <c r="O4" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3895</v>
+        <v>0.2608</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4715</v>
+        <v>0.182</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1299</v>
+        <v>0.0795</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1851</v>
+        <v>0.1135</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
@@ -1386,154 +1386,154 @@
         <v>37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0.53125</v>
+        <v>0.281</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5</v>
+        <v>0.2752</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.63</v>
+        <v>0.349</v>
       </c>
       <c r="AB4" t="n">
         <v>75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.73169</v>
+        <v>0.40722</v>
       </c>
       <c r="AD4" t="n">
         <v>75</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.63</v>
+        <v>0.349</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.722</v>
+        <v>0.397</v>
       </c>
       <c r="AH4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AU4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI4" t="n">
-        <v>0.4725</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AV4" t="n">
-        <v>0.3895</v>
+        <v>0.2608</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04511</v>
+        <v>0.02706</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.02083</v>
+        <v>0.0125</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.0625</v>
+        <v>0.4375</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.3895</v>
+        <v>0.2608</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.04511</v>
+        <v>0.02706</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02083</v>
+        <v>0.0125</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.469</v>
+        <v>0.312</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.0625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.786</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.786</v>
+        <v>0.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.0625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-04-04-06-NWO-FG</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/16-20 JIC x 7/16-20 JIC x 9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>1 1/16-12 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -1563,49 +1563,49 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hex / flats / bores from the Brennan TFA catalog p.59; JIC ends MS33656J; ORB branch end data from the table's own -06 ORB rows (A5) = the ORB library | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>legs differ from MS51529: AW [1.65, 1.65]+boss 1.94 vs MS 1.66/1.94 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.59 alone; marked DimSource BRENNAN | leg 3: adjustable ORB tip-to-body-face 0.75 = Air-Way 6801 ORB_I3 for -06 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-04-04-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-06-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="C5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="E5" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4365</v>
+        <v>0.2515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5965</v>
+        <v>0.2405</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1292</v>
+        <v>0.0898</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1858</v>
+        <v>0.1082</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1614,28 +1614,28 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="O5" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4365</v>
+        <v>0.2515</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5965</v>
+        <v>0.2405</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1292</v>
+        <v>0.0898</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1858</v>
+        <v>0.1082</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -1644,154 +1644,154 @@
         <v>37</v>
       </c>
       <c r="V5" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="X5" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6</v>
+        <v>0.2752</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.755</v>
+        <v>0.35</v>
       </c>
       <c r="AB5" t="n">
         <v>75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.87603</v>
+        <v>0.40837</v>
       </c>
       <c r="AD5" t="n">
         <v>75</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.755</v>
+        <v>0.35</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.866</v>
+        <v>0.397</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5975</v>
+        <v>0.2405</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.469</v>
+        <v>0.312</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.84</v>
+        <v>0.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.84</v>
+        <v>0.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.84</v>
+        <v>0.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.4365</v>
+        <v>0.2515</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.4365</v>
+        <v>0.2515</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.469</v>
+        <v>0.312</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.899</v>
+        <v>0.504</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.899</v>
+        <v>0.504</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-06-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 9/16-18 JIC x 9/16-18 JIC x 9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -1826,44 +1826,44 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p059-t02: agrees on LEG1@DRIVE, LEG2@DRIVE, LEG3@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE, D3@BORE | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 0.75 = Air-Way 6801 ORB_I3 for -06 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-06-06-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6803-20-20-20-NWO-FG</t>
+          <t>6803-10-10-10-NWO-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="E6" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4316</v>
+        <v>0.3553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.753</v>
+        <v>0.386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1288</v>
+        <v>0.1114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2382</v>
+        <v>0.1546</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -1872,28 +1872,28 @@
         <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4316</v>
+        <v>0.3553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.753</v>
+        <v>0.386</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1288</v>
+        <v>0.1114</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2382</v>
+        <v>0.1546</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
@@ -1902,192 +1902,966 @@
         <v>37</v>
       </c>
       <c r="V6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.945</v>
+        <v>0.505</v>
       </c>
       <c r="AB6" t="n">
         <v>75</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.09542</v>
+        <v>0.58735</v>
       </c>
       <c r="AD6" t="n">
         <v>75</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.945</v>
+        <v>0.505</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.0825</v>
+        <v>0.5775</v>
       </c>
       <c r="AH6" t="n">
         <v>0.05</v>
       </c>
       <c r="AI6" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>6803-10-10-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/8-14 JIC x 7/8-14 JIC x 7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>7/8-14 JIC</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>7/8-14 JIC</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1 = Air-Way 6801 ORB_I3 for -10 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>6803-10-10-10-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6803-12-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="T7" t="n">
+        <v>60</v>
+      </c>
+      <c r="U7" t="n">
+        <v>37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.73169</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>6803-12-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>legs differ from MS51529: AW [1.65, 1.65]+boss 1.94 vs MS 1.66/1.94 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>6803-12-12-12-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="n">
+        <v>37</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="T8" t="n">
+        <v>60</v>
+      </c>
+      <c r="U8" t="n">
+        <v>37</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.87603</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6803-20-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="n">
+        <v>37</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="T9" t="n">
+        <v>60</v>
+      </c>
+      <c r="U9" t="n">
+        <v>37</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.09542</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0.7534999999999999</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AJ9" t="n">
         <v>0.8125</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK9" t="n">
         <v>0.469</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL9" t="n">
         <v>1.88</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AM9" t="n">
         <v>0.41</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN9" t="n">
         <v>1.08</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AO9" t="n">
         <v>2.06</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP9" t="n">
         <v>1.08</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ9" t="n">
         <v>2.06</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR9" t="n">
         <v>1.08</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AS9" t="n">
         <v>2.25</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AT9" t="n">
         <v>1.625</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AU9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV9" t="n">
         <v>0.4316</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AW9" t="n">
         <v>0.04511</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AX9" t="n">
         <v>0.02083</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ9" t="n">
         <v>1.625</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BA9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB9" t="n">
         <v>0.4316</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC9" t="n">
         <v>0.04511</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD9" t="n">
         <v>0.02083</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BE9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BF9" t="n">
         <v>1.625</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BG9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BH9" t="n">
         <v>0.469</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BI9" t="n">
         <v>0.04511</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BJ9" t="n">
         <v>0.02083</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BK9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BL9" t="n">
         <v>1.63</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BM9" t="n">
         <v>1.102</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BN9" t="n">
         <v>1.102</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BO9" t="n">
         <v>1.63</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BP9" t="n">
         <v>1.11</v>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>6803-20-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/8-12 JIC x 1 5/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>6803</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -20 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>6803-20-20-20-NWO-FG</t>
         </is>
